--- a/ExcelDetails/SessionExcel.xlsx
+++ b/ExcelDetails/SessionExcel.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
   <si>
     <t>Date</t>
   </si>
@@ -250,6 +251,30 @@
   </si>
   <si>
     <t>EducationAIAgent/Session9 at develop · deveshomar/EducationAIAgent</t>
+  </si>
+  <si>
+    <t>Self imporving agent, Agent group chat, multi agent collabrations</t>
+  </si>
+  <si>
+    <t>Done with RAG Basic</t>
+  </si>
+  <si>
+    <t>Deep learning on vector and explained via plotting on graph</t>
+  </si>
+  <si>
+    <t>explained on Sementic search and keyword search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">explained consine similarity </t>
+  </si>
+  <si>
+    <t>Done with sample RAG</t>
+  </si>
+  <si>
+    <t>RAG and Done with Sample document policy -chunk and demo</t>
+  </si>
+  <si>
+    <t>ganesh chartuthi leave</t>
   </si>
 </sst>
 </file>
@@ -293,7 +318,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,6 +334,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -378,7 +409,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -414,28 +445,35 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -717,13 +755,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="85.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="112.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="112.44140625" style="19" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.44140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="25.33203125" style="1" customWidth="1"/>
@@ -736,7 +774,7 @@
       <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="19" t="s">
         <v>21</v>
       </c>
     </row>
@@ -749,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="7"/>
-      <c r="E2" s="26"/>
+      <c r="E2" s="20"/>
       <c r="F2" s="8" t="s">
         <v>4</v>
       </c>
@@ -761,7 +799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>37104</v>
       </c>
@@ -771,7 +809,7 @@
       <c r="D4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="21" t="s">
         <v>40</v>
       </c>
       <c r="F4" s="11" t="s">
@@ -792,7 +830,7 @@
       <c r="D5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="21" t="s">
         <v>42</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -807,7 +845,7 @@
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="28"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="16"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
@@ -817,16 +855,16 @@
       <c r="L6" s="15"/>
     </row>
     <row r="7" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="19">
+      <c r="A7" s="23">
         <v>37469</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="26" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="21" t="s">
         <v>34</v>
       </c>
       <c r="F7" s="11" t="s">
@@ -844,12 +882,12 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
-      <c r="C8" s="23"/>
+      <c r="A8" s="24"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="21" t="s">
         <v>36</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -860,21 +898,30 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="C9" s="24"/>
+      <c r="A9" s="25"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="21" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="12"/>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E10" s="27"/>
-      <c r="F10" s="12"/>
-      <c r="H10" s="13"/>
+    <row r="10" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
     </row>
     <row r="11" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
@@ -886,7 +933,7 @@
       <c r="D11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="21" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="9" t="s">
@@ -909,7 +956,7 @@
       <c r="D12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="21" t="s">
         <v>24</v>
       </c>
     </row>
@@ -917,192 +964,244 @@
       <c r="D13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
+    <row r="14" spans="1:12" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="23">
+        <v>40026</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="24"/>
+      <c r="C16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="19">
-        <v>40026</v>
-      </c>
+      <c r="A17" s="25"/>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="21" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
-      <c r="C18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="21"/>
-      <c r="C19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <v>42217</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E20" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F20" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G20" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="1" t="s">
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C21" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <v>42583</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E24" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F24" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G24" s="10" t="s">
         <v>55</v>
       </c>
     </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
+        <v>45139</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>45505</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
-        <v>45139</v>
-      </c>
       <c r="C29" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
-        <v>45505</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C31" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
         <v>47331</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
         <v>11171</v>
       </c>
     </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
+        <v>38596</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C38" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
-        <v>38596</v>
-      </c>
       <c r="C39" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E39" s="27" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C41" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C42" s="1" t="s">
-        <v>62</v>
+      <c r="E42" s="21" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="5">
+        <v>38961</v>
+      </c>
       <c r="C43" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E44" s="27" t="s">
-        <v>70</v>
+      <c r="C44" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="5">
-        <v>38961</v>
-      </c>
       <c r="C45" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C46" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C47" s="1" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
+        <v>41153</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="5">
+        <v>41518</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C51" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C53" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
+        <v>43344</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="5">
+        <v>43709</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="C7:C9"/>
-    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A15:A17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F4" r:id="rId1" display="https://us06web.zoom.us/rec/play/q3OlTzR3Wu8snSWsXZf_TWfb6SimMYV4PWE-HwfMcTLVHkSSvQvQldhdgPjSyLeIQyXrUJ1MMtI0sIpb.m6jOzod4n1Nj13k7?accessLevel=meeting&amp;canPlayFromShare=true&amp;from=my_recording&amp;continueMode=true&amp;oldStyle=true&amp;componentName=rec-play&amp;originRequestUrl=https%3A%2F%2Fus06web.zoom.us%2Frec%2Fshare%2F27AgOEsrmoVOEb-z2GY0NB5k8KJLa901-Z8nIJ9u4SKsHAfxh_HCVky0PXsefG5W.8b_L7eR4h5qPcPRj"/>
@@ -1117,15 +1216,15 @@
     <hyperlink ref="E9" r:id="rId10" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session2/ImageCreationOpenai/ImageCreationApp/ImageCreationApp"/>
     <hyperlink ref="E4" r:id="rId11" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session1/GoogleLLmIntegration/GoogleLLmIntegration"/>
     <hyperlink ref="E5" r:id="rId12" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session1/OpenAISample"/>
-    <hyperlink ref="E17" r:id="rId13" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session4"/>
-    <hyperlink ref="E18" r:id="rId14" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session4"/>
-    <hyperlink ref="E19" r:id="rId15" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session4"/>
-    <hyperlink ref="F26" r:id="rId16"/>
-    <hyperlink ref="F22" r:id="rId17" display="https://us06web.zoom.us/rec/share/VsNS9yfjeiwoVhZZ_yvjY49o86dR1LOIa8lGiHMUx84nstPASy_9-y_enlCANPQW.ZfMKuV-ypV2lSfFN"/>
-    <hyperlink ref="E26" r:id="rId18" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session6"/>
-    <hyperlink ref="E22" r:id="rId19" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session5"/>
-    <hyperlink ref="E44" r:id="rId20" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session10"/>
-    <hyperlink ref="E39" r:id="rId21" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session9"/>
+    <hyperlink ref="E15" r:id="rId13" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session4"/>
+    <hyperlink ref="E16" r:id="rId14" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session4"/>
+    <hyperlink ref="E17" r:id="rId15" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session4"/>
+    <hyperlink ref="F24" r:id="rId16"/>
+    <hyperlink ref="F20" r:id="rId17" display="https://us06web.zoom.us/rec/share/VsNS9yfjeiwoVhZZ_yvjY49o86dR1LOIa8lGiHMUx84nstPASy_9-y_enlCANPQW.ZfMKuV-ypV2lSfFN"/>
+    <hyperlink ref="E24" r:id="rId18" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session6"/>
+    <hyperlink ref="E20" r:id="rId19" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session5"/>
+    <hyperlink ref="E42" r:id="rId20" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session10"/>
+    <hyperlink ref="E37" r:id="rId21" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId22"/>
